--- a/GERADOR DE DOCUMENTOS/SCRIPTS/Planilha_Municipios.xlsx
+++ b/GERADOR DE DOCUMENTOS/SCRIPTS/Planilha_Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\GERADOR DE DOCUMENTOS\SCRIPTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53359B24-A49D-41A4-8B2D-B65D19F1D632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07241B28-7D4E-46EC-80AC-4D097526B681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="578">
   <si>
     <t>_arquivo_origem</t>
   </si>
@@ -1759,13 +1759,50 @@
   </si>
   <si>
     <t>ouvidoria@saomamede.pb.gov.br</t>
+  </si>
+  <si>
+    <t>Dados_Nova_Ibia.tex</t>
+  </si>
+  <si>
+    <t>Nova Ibiá</t>
+  </si>
+  <si>
+    <t>3469025</t>
+  </si>
+  <si>
+    <t>Praça São José, nº 88, Centro, Nova Ibiá – BA, CEP 45452-000</t>
+  </si>
+  <si>
+    <t>Marcio Tarantine Souza Sampaio</t>
+  </si>
+  <si>
+    <t>076/2025</t>
+  </si>
+  <si>
+    <t>Diário Oficial Eletrônico</t>
+  </si>
+  <si>
+    <t>14 de Março de 2025</t>
+  </si>
+  <si>
+    <t>[...]
+Deverá a empresa efetuar levantamento dos créditos a que faz jus o Município, referentes aos pagamentos indevidos à concessionária de energia elétrica, conforme os prazos estabelecidos na Resolução Normativa da ANEEL nº 1.000, de 7 de dezembro de 2021, especialmente o art. 323, § 2º, inciso I, e suas alterações posteriores, podendo, para tanto, representar administrativamente o Município de Nova Ibiá/BA perante a Agência Nacional de Energia Elétrica — ANEEL, em todos os processos, reclamações, recursos e demais atos decorrentes de suas competências.</t>
+  </si>
+  <si>
+    <t>(73) 3653-1177</t>
+  </si>
+  <si>
+    <t>prefeitura@novaibia.ba.gov.br</t>
+  </si>
+  <si>
+    <t>32.697.583/0001-48</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1789,6 +1826,12 @@
       <sz val="10"/>
       <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1841,7 +1884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1855,6 +1898,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2219,7 +2266,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="36" customWidth="1"/>
@@ -4714,6 +4761,65 @@
       </c>
       <c r="S42" s="3" t="s">
         <v>495</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>566</v>
+      </c>
+      <c r="B43" t="s">
+        <v>525</v>
+      </c>
+      <c r="C43" t="s">
+        <v>546</v>
+      </c>
+      <c r="D43" t="s">
+        <v>567</v>
+      </c>
+      <c r="E43" t="s">
+        <v>577</v>
+      </c>
+      <c r="F43" t="s">
+        <v>575</v>
+      </c>
+      <c r="G43" t="s">
+        <v>576</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I43" t="s">
+        <v>568</v>
+      </c>
+      <c r="J43" t="s">
+        <v>569</v>
+      </c>
+      <c r="K43" t="s">
+        <v>570</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43" t="s">
+        <v>571</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>573</v>
+      </c>
+      <c r="R43" t="s">
+        <v>128</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>574</v>
       </c>
     </row>
   </sheetData>
